--- a/WindowsFormsApplication/WindowsFormsApplication/Template/TestDbc/FE3153GntExcelDbcFromTxt.xlsx
+++ b/WindowsFormsApplication/WindowsFormsApplication/Template/TestDbc/FE3153GntExcelDbcFromTxt.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1854" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1851" uniqueCount="273">
   <si>
     <t>SigName</t>
   </si>
@@ -2421,7 +2421,7 @@
   <dimension ref="A1:R109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="34.25" customWidth="1"/>
+    <col min="1" max="1" width="58.75" customWidth="1"/>
     <col min="7" max="7" width="11.125" customWidth="1"/>
     <col min="9" max="9" width="20.625" customWidth="1"/>
     <col min="10" max="10" width="22.875" customWidth="1"/>
@@ -2500,8 +2500,8 @@
       <c r="E2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" t="s">
-        <v>23</v>
+      <c r="F2">
+        <v>1000</v>
       </c>
       <c r="H2" t="s">
         <v>23</v>
@@ -2553,8 +2553,8 @@
       <c r="E3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s">
-        <v>23</v>
+      <c r="F3">
+        <v>1000</v>
       </c>
       <c r="H3" t="s">
         <v>23</v>
@@ -2606,8 +2606,8 @@
       <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="F4" t="s">
-        <v>23</v>
+      <c r="F4">
+        <v>1000</v>
       </c>
       <c r="H4" t="s">
         <v>23</v>
@@ -2662,7 +2662,6 @@
       <c r="F5" t="s">
         <v>37</v>
       </c>
-      <c r="G5"/>
       <c r="H5" t="s">
         <v>23</v>
       </c>
@@ -2716,7 +2715,6 @@
       <c r="F6" t="s">
         <v>37</v>
       </c>
-      <c r="G6"/>
       <c r="H6" t="s">
         <v>23</v>
       </c>
@@ -2770,7 +2768,6 @@
       <c r="F7" t="s">
         <v>37</v>
       </c>
-      <c r="G7"/>
       <c r="H7" t="s">
         <v>23</v>
       </c>
@@ -2877,7 +2874,6 @@
       <c r="F9" t="s">
         <v>37</v>
       </c>
-      <c r="G9"/>
       <c r="H9" t="s">
         <v>23</v>
       </c>
@@ -2931,7 +2927,6 @@
       <c r="F10" t="s">
         <v>37</v>
       </c>
-      <c r="G10"/>
       <c r="H10" t="s">
         <v>23</v>
       </c>
@@ -2985,7 +2980,6 @@
       <c r="F11" t="s">
         <v>37</v>
       </c>
-      <c r="G11"/>
       <c r="H11" t="s">
         <v>23</v>
       </c>
@@ -3092,7 +3086,6 @@
       <c r="F13" t="s">
         <v>37</v>
       </c>
-      <c r="G13"/>
       <c r="H13" t="s">
         <v>23</v>
       </c>
@@ -3146,7 +3139,6 @@
       <c r="F14" t="s">
         <v>37</v>
       </c>
-      <c r="G14"/>
       <c r="H14" t="s">
         <v>23</v>
       </c>
@@ -3200,7 +3192,6 @@
       <c r="F15" t="s">
         <v>37</v>
       </c>
-      <c r="G15"/>
       <c r="H15" t="s">
         <v>23</v>
       </c>
@@ -3254,7 +3245,6 @@
       <c r="F16" t="s">
         <v>37</v>
       </c>
-      <c r="G16"/>
       <c r="H16" t="s">
         <v>23</v>
       </c>
@@ -3308,7 +3298,6 @@
       <c r="F17" t="s">
         <v>37</v>
       </c>
-      <c r="G17"/>
       <c r="H17" t="s">
         <v>23</v>
       </c>
@@ -3362,7 +3351,6 @@
       <c r="F18" t="s">
         <v>37</v>
       </c>
-      <c r="G18"/>
       <c r="H18" t="s">
         <v>23</v>
       </c>
@@ -3416,7 +3404,6 @@
       <c r="F19" t="s">
         <v>37</v>
       </c>
-      <c r="G19"/>
       <c r="H19" t="s">
         <v>23</v>
       </c>
@@ -3470,7 +3457,6 @@
       <c r="F20" t="s">
         <v>37</v>
       </c>
-      <c r="G20"/>
       <c r="H20" t="s">
         <v>23</v>
       </c>
@@ -3524,7 +3510,6 @@
       <c r="F21" t="s">
         <v>37</v>
       </c>
-      <c r="G21"/>
       <c r="H21" t="s">
         <v>23</v>
       </c>
@@ -3578,7 +3563,6 @@
       <c r="F22" t="s">
         <v>37</v>
       </c>
-      <c r="G22"/>
       <c r="H22" t="s">
         <v>23</v>
       </c>
@@ -3632,7 +3616,6 @@
       <c r="F23" t="s">
         <v>37</v>
       </c>
-      <c r="G23"/>
       <c r="H23" t="s">
         <v>23</v>
       </c>
@@ -3686,7 +3669,6 @@
       <c r="F24" t="s">
         <v>37</v>
       </c>
-      <c r="G24"/>
       <c r="H24" t="s">
         <v>23</v>
       </c>
@@ -3740,7 +3722,6 @@
       <c r="F25" t="s">
         <v>37</v>
       </c>
-      <c r="G25"/>
       <c r="H25" t="s">
         <v>23</v>
       </c>
@@ -3794,7 +3775,6 @@
       <c r="F26" t="s">
         <v>37</v>
       </c>
-      <c r="G26"/>
       <c r="H26" t="s">
         <v>23</v>
       </c>
@@ -3848,7 +3828,6 @@
       <c r="F27" t="s">
         <v>37</v>
       </c>
-      <c r="G27"/>
       <c r="H27" t="s">
         <v>23</v>
       </c>
@@ -3955,7 +3934,6 @@
       <c r="F29" t="s">
         <v>37</v>
       </c>
-      <c r="G29"/>
       <c r="H29" t="s">
         <v>23</v>
       </c>
@@ -4009,7 +3987,6 @@
       <c r="F30" t="s">
         <v>37</v>
       </c>
-      <c r="G30"/>
       <c r="H30" t="s">
         <v>23</v>
       </c>
@@ -4063,7 +4040,6 @@
       <c r="F31" t="s">
         <v>37</v>
       </c>
-      <c r="G31"/>
       <c r="H31" t="s">
         <v>23</v>
       </c>
@@ -4117,7 +4093,6 @@
       <c r="F32" t="s">
         <v>37</v>
       </c>
-      <c r="G32"/>
       <c r="H32" t="s">
         <v>23</v>
       </c>
@@ -4171,7 +4146,6 @@
       <c r="F33" t="s">
         <v>37</v>
       </c>
-      <c r="G33"/>
       <c r="H33" t="s">
         <v>23</v>
       </c>
@@ -4225,7 +4199,6 @@
       <c r="F34" t="s">
         <v>37</v>
       </c>
-      <c r="G34"/>
       <c r="H34" t="s">
         <v>23</v>
       </c>
@@ -4279,7 +4252,6 @@
       <c r="F35" t="s">
         <v>37</v>
       </c>
-      <c r="G35"/>
       <c r="H35" t="s">
         <v>23</v>
       </c>
@@ -4333,7 +4305,6 @@
       <c r="F36" t="s">
         <v>37</v>
       </c>
-      <c r="G36"/>
       <c r="H36" t="s">
         <v>23</v>
       </c>
@@ -4387,7 +4358,6 @@
       <c r="F37" t="s">
         <v>37</v>
       </c>
-      <c r="G37"/>
       <c r="H37" t="s">
         <v>23</v>
       </c>
@@ -4494,7 +4464,6 @@
       <c r="F39" t="s">
         <v>37</v>
       </c>
-      <c r="G39"/>
       <c r="H39" t="s">
         <v>23</v>
       </c>
@@ -4548,7 +4517,6 @@
       <c r="F40" t="s">
         <v>37</v>
       </c>
-      <c r="G40"/>
       <c r="H40" t="s">
         <v>23</v>
       </c>
@@ -4602,7 +4570,6 @@
       <c r="F41" t="s">
         <v>37</v>
       </c>
-      <c r="G41"/>
       <c r="H41" t="s">
         <v>23</v>
       </c>
@@ -4656,7 +4623,6 @@
       <c r="F42" t="s">
         <v>37</v>
       </c>
-      <c r="G42"/>
       <c r="H42" t="s">
         <v>23</v>
       </c>
@@ -4710,7 +4676,6 @@
       <c r="F43" t="s">
         <v>37</v>
       </c>
-      <c r="G43"/>
       <c r="H43" t="s">
         <v>23</v>
       </c>
@@ -4764,7 +4729,6 @@
       <c r="F44" t="s">
         <v>37</v>
       </c>
-      <c r="G44"/>
       <c r="H44" t="s">
         <v>23</v>
       </c>
@@ -4818,7 +4782,6 @@
       <c r="F45" t="s">
         <v>37</v>
       </c>
-      <c r="G45"/>
       <c r="H45" t="s">
         <v>23</v>
       </c>
@@ -4925,7 +4888,6 @@
       <c r="F47" t="s">
         <v>37</v>
       </c>
-      <c r="G47"/>
       <c r="H47" t="s">
         <v>23</v>
       </c>
@@ -4979,7 +4941,6 @@
       <c r="F48" t="s">
         <v>153</v>
       </c>
-      <c r="G48"/>
       <c r="H48" t="s">
         <v>23</v>
       </c>
@@ -5033,7 +4994,6 @@
       <c r="F49" t="s">
         <v>153</v>
       </c>
-      <c r="G49"/>
       <c r="H49" t="s">
         <v>23</v>
       </c>
@@ -5087,7 +5047,6 @@
       <c r="F50" t="s">
         <v>153</v>
       </c>
-      <c r="G50"/>
       <c r="H50" t="s">
         <v>23</v>
       </c>
@@ -5300,7 +5259,6 @@
       <c r="F54" t="s">
         <v>160</v>
       </c>
-      <c r="G54"/>
       <c r="H54" t="s">
         <v>23</v>
       </c>
@@ -5354,7 +5312,6 @@
       <c r="F55" t="s">
         <v>160</v>
       </c>
-      <c r="G55"/>
       <c r="H55" t="s">
         <v>23</v>
       </c>
@@ -5408,7 +5365,6 @@
       <c r="F56" t="s">
         <v>160</v>
       </c>
-      <c r="G56"/>
       <c r="H56" t="s">
         <v>23</v>
       </c>
@@ -5462,7 +5418,6 @@
       <c r="F57" t="s">
         <v>160</v>
       </c>
-      <c r="G57"/>
       <c r="H57" t="s">
         <v>23</v>
       </c>
@@ -5516,7 +5471,6 @@
       <c r="F58" t="s">
         <v>160</v>
       </c>
-      <c r="G58"/>
       <c r="H58" t="s">
         <v>23</v>
       </c>
@@ -5570,7 +5524,6 @@
       <c r="F59" t="s">
         <v>160</v>
       </c>
-      <c r="G59"/>
       <c r="H59" t="s">
         <v>23</v>
       </c>
@@ -5624,7 +5577,6 @@
       <c r="F60" t="s">
         <v>160</v>
       </c>
-      <c r="G60"/>
       <c r="H60" t="s">
         <v>23</v>
       </c>
@@ -5678,7 +5630,6 @@
       <c r="F61" t="s">
         <v>160</v>
       </c>
-      <c r="G61"/>
       <c r="H61" t="s">
         <v>23</v>
       </c>
@@ -5838,7 +5789,6 @@
       <c r="F64" t="s">
         <v>160</v>
       </c>
-      <c r="G64"/>
       <c r="H64" t="s">
         <v>23</v>
       </c>
@@ -5945,7 +5895,6 @@
       <c r="F66" t="s">
         <v>37</v>
       </c>
-      <c r="G66"/>
       <c r="H66" t="s">
         <v>23</v>
       </c>
@@ -5999,7 +5948,6 @@
       <c r="F67" t="s">
         <v>103</v>
       </c>
-      <c r="G67"/>
       <c r="H67" t="s">
         <v>23</v>
       </c>
@@ -6053,7 +6001,6 @@
       <c r="F68" t="s">
         <v>103</v>
       </c>
-      <c r="G68"/>
       <c r="H68" t="s">
         <v>23</v>
       </c>
@@ -6107,7 +6054,6 @@
       <c r="F69" t="s">
         <v>103</v>
       </c>
-      <c r="G69"/>
       <c r="H69" t="s">
         <v>23</v>
       </c>
@@ -6161,7 +6107,6 @@
       <c r="F70" t="s">
         <v>103</v>
       </c>
-      <c r="G70"/>
       <c r="H70" t="s">
         <v>23</v>
       </c>
@@ -6215,7 +6160,6 @@
       <c r="F71" t="s">
         <v>103</v>
       </c>
-      <c r="G71"/>
       <c r="H71" t="s">
         <v>23</v>
       </c>
@@ -6269,7 +6213,6 @@
       <c r="F72" t="s">
         <v>103</v>
       </c>
-      <c r="G72"/>
       <c r="H72" t="s">
         <v>23</v>
       </c>
@@ -6323,7 +6266,6 @@
       <c r="F73" t="s">
         <v>103</v>
       </c>
-      <c r="G73"/>
       <c r="H73" t="s">
         <v>23</v>
       </c>
@@ -6377,7 +6319,6 @@
       <c r="F74" t="s">
         <v>103</v>
       </c>
-      <c r="G74"/>
       <c r="H74" t="s">
         <v>23</v>
       </c>
@@ -6431,7 +6372,6 @@
       <c r="F75" t="s">
         <v>103</v>
       </c>
-      <c r="G75"/>
       <c r="H75" t="s">
         <v>23</v>
       </c>
@@ -6485,7 +6425,6 @@
       <c r="F76" t="s">
         <v>103</v>
       </c>
-      <c r="G76"/>
       <c r="H76" t="s">
         <v>23</v>
       </c>
@@ -6539,7 +6478,6 @@
       <c r="F77" t="s">
         <v>37</v>
       </c>
-      <c r="G77"/>
       <c r="H77" t="s">
         <v>23</v>
       </c>
@@ -6593,7 +6531,6 @@
       <c r="F78" t="s">
         <v>37</v>
       </c>
-      <c r="G78"/>
       <c r="H78" t="s">
         <v>23</v>
       </c>
@@ -6647,7 +6584,6 @@
       <c r="F79" t="s">
         <v>37</v>
       </c>
-      <c r="G79"/>
       <c r="H79" t="s">
         <v>23</v>
       </c>
@@ -6701,7 +6637,6 @@
       <c r="F80" t="s">
         <v>37</v>
       </c>
-      <c r="G80"/>
       <c r="H80" t="s">
         <v>23</v>
       </c>
@@ -6755,7 +6690,6 @@
       <c r="F81" t="s">
         <v>37</v>
       </c>
-      <c r="G81"/>
       <c r="H81" t="s">
         <v>23</v>
       </c>
@@ -6809,7 +6743,6 @@
       <c r="F82" t="s">
         <v>37</v>
       </c>
-      <c r="G82"/>
       <c r="H82" t="s">
         <v>23</v>
       </c>
@@ -6863,7 +6796,6 @@
       <c r="F83" t="s">
         <v>37</v>
       </c>
-      <c r="G83"/>
       <c r="H83" t="s">
         <v>23</v>
       </c>
@@ -6917,7 +6849,6 @@
       <c r="F84" t="s">
         <v>37</v>
       </c>
-      <c r="G84"/>
       <c r="H84" t="s">
         <v>23</v>
       </c>
@@ -6971,7 +6902,6 @@
       <c r="F85" t="s">
         <v>37</v>
       </c>
-      <c r="G85"/>
       <c r="H85" t="s">
         <v>23</v>
       </c>
@@ -7025,7 +6955,6 @@
       <c r="F86" t="s">
         <v>37</v>
       </c>
-      <c r="G86"/>
       <c r="H86" t="s">
         <v>23</v>
       </c>
@@ -7079,7 +7008,6 @@
       <c r="F87" t="s">
         <v>37</v>
       </c>
-      <c r="G87"/>
       <c r="H87" t="s">
         <v>23</v>
       </c>
@@ -7133,7 +7061,6 @@
       <c r="F88" t="s">
         <v>37</v>
       </c>
-      <c r="G88"/>
       <c r="H88" t="s">
         <v>23</v>
       </c>
@@ -7187,7 +7114,6 @@
       <c r="F89" t="s">
         <v>37</v>
       </c>
-      <c r="G89"/>
       <c r="H89" t="s">
         <v>23</v>
       </c>
@@ -7241,7 +7167,6 @@
       <c r="F90" t="s">
         <v>37</v>
       </c>
-      <c r="G90"/>
       <c r="H90" t="s">
         <v>23</v>
       </c>
@@ -7295,7 +7220,6 @@
       <c r="F91" t="s">
         <v>37</v>
       </c>
-      <c r="G91"/>
       <c r="H91" t="s">
         <v>23</v>
       </c>
@@ -7349,7 +7273,6 @@
       <c r="F92" t="s">
         <v>37</v>
       </c>
-      <c r="G92"/>
       <c r="H92" t="s">
         <v>23</v>
       </c>
@@ -7403,7 +7326,6 @@
       <c r="F93" t="s">
         <v>37</v>
       </c>
-      <c r="G93"/>
       <c r="H93" t="s">
         <v>23</v>
       </c>
@@ -7457,7 +7379,6 @@
       <c r="F94" t="s">
         <v>37</v>
       </c>
-      <c r="G94"/>
       <c r="H94" t="s">
         <v>23</v>
       </c>
@@ -7511,7 +7432,6 @@
       <c r="F95" t="s">
         <v>37</v>
       </c>
-      <c r="G95"/>
       <c r="H95" t="s">
         <v>23</v>
       </c>
@@ -7565,7 +7485,6 @@
       <c r="F96" t="s">
         <v>37</v>
       </c>
-      <c r="G96"/>
       <c r="H96" t="s">
         <v>23</v>
       </c>
@@ -7619,7 +7538,6 @@
       <c r="F97" t="s">
         <v>37</v>
       </c>
-      <c r="G97"/>
       <c r="H97" t="s">
         <v>23</v>
       </c>
@@ -7673,7 +7591,6 @@
       <c r="F98" t="s">
         <v>37</v>
       </c>
-      <c r="G98"/>
       <c r="H98" t="s">
         <v>23</v>
       </c>
@@ -7727,7 +7644,6 @@
       <c r="F99" t="s">
         <v>37</v>
       </c>
-      <c r="G99"/>
       <c r="H99" t="s">
         <v>23</v>
       </c>
@@ -7781,7 +7697,6 @@
       <c r="F100" t="s">
         <v>37</v>
       </c>
-      <c r="G100"/>
       <c r="H100" t="s">
         <v>23</v>
       </c>
@@ -7835,7 +7750,6 @@
       <c r="F101" t="s">
         <v>37</v>
       </c>
-      <c r="G101"/>
       <c r="H101" t="s">
         <v>23</v>
       </c>
@@ -7889,7 +7803,6 @@
       <c r="F102" t="s">
         <v>37</v>
       </c>
-      <c r="G102"/>
       <c r="H102" t="s">
         <v>23</v>
       </c>
@@ -7943,7 +7856,6 @@
       <c r="F103" t="s">
         <v>37</v>
       </c>
-      <c r="G103"/>
       <c r="H103" t="s">
         <v>23</v>
       </c>
@@ -7997,7 +7909,6 @@
       <c r="F104" t="s">
         <v>103</v>
       </c>
-      <c r="G104"/>
       <c r="H104" t="s">
         <v>23</v>
       </c>
@@ -8051,7 +7962,6 @@
       <c r="F105" t="s">
         <v>103</v>
       </c>
-      <c r="G105"/>
       <c r="H105" t="s">
         <v>23</v>
       </c>
@@ -8105,7 +8015,6 @@
       <c r="F106" t="s">
         <v>103</v>
       </c>
-      <c r="G106"/>
       <c r="H106" t="s">
         <v>23</v>
       </c>
@@ -8159,7 +8068,6 @@
       <c r="F107" t="s">
         <v>103</v>
       </c>
-      <c r="G107"/>
       <c r="H107" t="s">
         <v>23</v>
       </c>
@@ -8213,7 +8121,6 @@
       <c r="F108" t="s">
         <v>103</v>
       </c>
-      <c r="G108"/>
       <c r="H108" t="s">
         <v>23</v>
       </c>
@@ -8267,7 +8174,6 @@
       <c r="F109" t="s">
         <v>103</v>
       </c>
-      <c r="G109"/>
       <c r="H109" t="s">
         <v>23</v>
       </c>
